--- a/OMOP TO CLIF.xlsx
+++ b/OMOP TO CLIF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dariushmokhlesi/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E244BBFD-093F-7F4D-AA82-82BD3B05F9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B045DDC-8444-EC43-B430-C927686073E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="760" windowWidth="17700" windowHeight="17860" xr2:uid="{4817317C-EEFD-2545-985F-347F5DD65845}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20960" windowHeight="20120" xr2:uid="{4817317C-EEFD-2545-985F-347F5DD65845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="128">
   <si>
     <t>person</t>
   </si>
@@ -233,9 +233,6 @@
     <t>vital_value</t>
   </si>
   <si>
-    <t>value_as_concept_Id</t>
-  </si>
-  <si>
     <t>meas_site_name</t>
   </si>
   <si>
@@ -375,6 +372,54 @@
   </si>
   <si>
     <t>mar_action_category</t>
+  </si>
+  <si>
+    <t>death_dttm</t>
+  </si>
+  <si>
+    <t>language_category</t>
+  </si>
+  <si>
+    <t>ethnicity_name</t>
+  </si>
+  <si>
+    <t>race_name</t>
+  </si>
+  <si>
+    <t>sex_name</t>
+  </si>
+  <si>
+    <t>language_name</t>
+  </si>
+  <si>
+    <t>hospitalization_joined_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> zipcode_nine_digit</t>
+  </si>
+  <si>
+    <t>zipcode_five_digit</t>
+  </si>
+  <si>
+    <t>census_block_code</t>
+  </si>
+  <si>
+    <t>census_block_group_code</t>
+  </si>
+  <si>
+    <t>census_tract</t>
+  </si>
+  <si>
+    <t>state_code</t>
+  </si>
+  <si>
+    <t>county_code</t>
+  </si>
+  <si>
+    <t>age_at_admission</t>
+  </si>
+  <si>
+    <t>value_as_concept_id</t>
   </si>
 </sst>
 </file>
@@ -409,12 +454,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -429,11 +480,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743A751C-91B0-C04E-ADC9-F5B6DE3B4401}">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -823,13 +878,13 @@
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -837,13 +892,13 @@
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -851,13 +906,13 @@
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -872,7 +927,7 @@
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -946,17 +1001,17 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D13" t="s">
-        <v>18</v>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -970,20 +1025,20 @@
         <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -998,20 +1053,20 @@
         <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1026,63 +1081,63 @@
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1090,13 +1145,13 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1104,13 +1159,13 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1118,13 +1173,13 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1132,13 +1187,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1146,13 +1201,13 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1160,13 +1215,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
         <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1174,13 +1229,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -1188,13 +1243,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1202,7 +1257,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
@@ -1216,7 +1271,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
@@ -1230,7 +1285,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
         <v>30</v>
@@ -1240,31 +1295,31 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
+      <c r="A34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" t="s">
-        <v>51</v>
+      <c r="A35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1272,727 +1327,895 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
-      </c>
-      <c r="D47" t="s">
-        <v>68</v>
+        <v>30</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C61" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="D61" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B62" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C64" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="D64" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B65" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C50" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" t="s">
-        <v>54</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C88" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" t="s">
-        <v>54</v>
-      </c>
-      <c r="D53" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" t="s">
-        <v>54</v>
-      </c>
-      <c r="D55" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" t="s">
-        <v>75</v>
-      </c>
-      <c r="C56" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" t="s">
-        <v>78</v>
-      </c>
-      <c r="C59" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>80</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" t="s">
-        <v>101</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>80</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" t="s">
-        <v>101</v>
-      </c>
-      <c r="D61" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>80</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" t="s">
-        <v>101</v>
-      </c>
-      <c r="D62" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C63" t="s">
-        <v>101</v>
-      </c>
-      <c r="D63" s="3" t="s">
+    <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>80</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C64" t="s">
-        <v>101</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>80</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>101</v>
-      </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>80</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" t="s">
-        <v>101</v>
-      </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" t="s">
-        <v>101</v>
-      </c>
-      <c r="D68" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>80</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" t="s">
-        <v>101</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70" t="s">
-        <v>101</v>
-      </c>
-      <c r="D70" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C71" t="s">
-        <v>101</v>
-      </c>
-      <c r="D71" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" t="s">
-        <v>101</v>
-      </c>
-      <c r="D72" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C73" t="s">
-        <v>101</v>
-      </c>
-      <c r="D73" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C74" t="s">
-        <v>101</v>
-      </c>
-      <c r="D74" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>80</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C75" t="s">
-        <v>101</v>
-      </c>
-      <c r="D75" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>80</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C76" t="s">
-        <v>101</v>
-      </c>
-      <c r="D76" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" t="s">
-        <v>101</v>
-      </c>
-      <c r="D77" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>80</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C78" t="s">
-        <v>101</v>
-      </c>
-      <c r="D78" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C79" t="s">
-        <v>101</v>
-      </c>
-      <c r="D79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>80</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C80" t="s">
-        <v>101</v>
-      </c>
-      <c r="D80" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" t="s">
-        <v>101</v>
-      </c>
-      <c r="D81" t="s">
+    <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C82" t="s">
-        <v>101</v>
-      </c>
-      <c r="D82" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>80</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C83" t="s">
-        <v>101</v>
-      </c>
-      <c r="D83" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>80</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C84" t="s">
-        <v>101</v>
-      </c>
-      <c r="D84" t="s">
+    <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>80</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C85" t="s">
-        <v>101</v>
-      </c>
-      <c r="D85" t="s">
+    <row r="98" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>80</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C86" t="s">
-        <v>101</v>
-      </c>
-      <c r="D86" t="s">
+    <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C87" t="s">
-        <v>101</v>
-      </c>
-      <c r="D87" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
